--- a/no-basis/CurrentBuild/ValueSet-no-basis-service-type.valueset.xlsx
+++ b/no-basis/CurrentBuild/ValueSet-no-basis-service-type.valueset.xlsx
@@ -7,20 +7,20 @@
   </bookViews>
   <sheets>
     <sheet name="Metadata" r:id="rId3" sheetId="1"/>
-    <sheet name="Include from unknown" r:id="rId4" sheetId="2"/>
-    <sheet name="Include from unknown 2" r:id="rId5" sheetId="3"/>
-    <sheet name="Include from unknown 3" r:id="rId6" sheetId="4"/>
-    <sheet name="Include from unknown 4" r:id="rId7" sheetId="5"/>
-    <sheet name="Include from unknown 5" r:id="rId8" sheetId="6"/>
-    <sheet name="Include from unknown 6" r:id="rId9" sheetId="7"/>
-    <sheet name="Include from unknown 7" r:id="rId10" sheetId="8"/>
-    <sheet name="Include from unknown 8" r:id="rId11" sheetId="9"/>
+    <sheet name="Include #0" r:id="rId4" sheetId="2"/>
+    <sheet name="Include #1" r:id="rId5" sheetId="3"/>
+    <sheet name="Include #2" r:id="rId6" sheetId="4"/>
+    <sheet name="Include #3" r:id="rId7" sheetId="5"/>
+    <sheet name="Include #4" r:id="rId8" sheetId="6"/>
+    <sheet name="Include #5" r:id="rId9" sheetId="7"/>
+    <sheet name="Include #6" r:id="rId10" sheetId="8"/>
+    <sheet name="Include #7" r:id="rId11" sheetId="9"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="37">
   <si>
     <t>Property</t>
   </si>
@@ -71,9 +71,6 @@
   </si>
   <si>
     <t>Publisher</t>
-  </si>
-  <si>
-    <t>Direktoratet for e-helse</t>
   </si>
   <si>
     <t>Jurisdiction</t>
@@ -342,44 +339,42 @@
       <c r="A9" t="s" s="2">
         <v>16</v>
       </c>
-      <c r="B9" t="s" s="2">
-        <v>17</v>
-      </c>
+      <c r="B9" s="2"/>
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
+        <v>17</v>
+      </c>
+      <c r="B10" t="s" s="2">
         <v>18</v>
-      </c>
-      <c r="B10" t="s" s="2">
-        <v>19</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="B11" t="s" s="2">
         <v>20</v>
-      </c>
-      <c r="B11" t="s" s="2">
-        <v>21</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B12" s="2"/>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B13" s="2"/>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="B14" t="s" s="2">
         <v>24</v>
-      </c>
-      <c r="B14" t="s" s="2">
-        <v>25</v>
       </c>
     </row>
   </sheetData>
@@ -398,28 +393,28 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s" s="2">
         <v>26</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="s" s="2">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="s" s="2">
+    <row r="3">
+      <c r="A3" t="s" s="2">
+        <v>27</v>
+      </c>
+      <c r="B3" t="s" s="2">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s" s="2">
         <v>28</v>
       </c>
-      <c r="B3" t="s" s="2">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="s" s="2">
+      <c r="B4" t="s" s="2">
         <v>29</v>
-      </c>
-      <c r="B4" t="s" s="2">
-        <v>30</v>
       </c>
     </row>
   </sheetData>
@@ -438,28 +433,28 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s" s="2">
         <v>26</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="s" s="2">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="s" s="2">
+    <row r="3">
+      <c r="A3" t="s" s="2">
+        <v>27</v>
+      </c>
+      <c r="B3" t="s" s="2">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s" s="2">
         <v>28</v>
       </c>
-      <c r="B3" t="s" s="2">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="s" s="2">
-        <v>29</v>
-      </c>
-      <c r="B4" t="s" s="2">
-        <v>31</v>
+      <c r="B4" t="s" s="2">
+        <v>30</v>
       </c>
     </row>
   </sheetData>
@@ -478,28 +473,28 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s" s="2">
         <v>26</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="s" s="2">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="s" s="2">
+    <row r="3">
+      <c r="A3" t="s" s="2">
+        <v>27</v>
+      </c>
+      <c r="B3" t="s" s="2">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s" s="2">
         <v>28</v>
       </c>
-      <c r="B3" t="s" s="2">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="s" s="2">
-        <v>29</v>
-      </c>
-      <c r="B4" t="s" s="2">
-        <v>32</v>
+      <c r="B4" t="s" s="2">
+        <v>31</v>
       </c>
     </row>
   </sheetData>
@@ -518,28 +513,28 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s" s="2">
         <v>26</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="s" s="2">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="s" s="2">
+    <row r="3">
+      <c r="A3" t="s" s="2">
+        <v>27</v>
+      </c>
+      <c r="B3" t="s" s="2">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s" s="2">
         <v>28</v>
       </c>
-      <c r="B3" t="s" s="2">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="s" s="2">
-        <v>29</v>
-      </c>
-      <c r="B4" t="s" s="2">
-        <v>33</v>
+      <c r="B4" t="s" s="2">
+        <v>32</v>
       </c>
     </row>
   </sheetData>
@@ -558,28 +553,28 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s" s="2">
         <v>26</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="s" s="2">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="s" s="2">
+    <row r="3">
+      <c r="A3" t="s" s="2">
+        <v>27</v>
+      </c>
+      <c r="B3" t="s" s="2">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s" s="2">
         <v>28</v>
       </c>
-      <c r="B3" t="s" s="2">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="s" s="2">
-        <v>29</v>
-      </c>
-      <c r="B4" t="s" s="2">
-        <v>34</v>
+      <c r="B4" t="s" s="2">
+        <v>33</v>
       </c>
     </row>
   </sheetData>
@@ -598,28 +593,28 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s" s="2">
         <v>26</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="s" s="2">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="s" s="2">
+    <row r="3">
+      <c r="A3" t="s" s="2">
+        <v>27</v>
+      </c>
+      <c r="B3" t="s" s="2">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s" s="2">
         <v>28</v>
       </c>
-      <c r="B3" t="s" s="2">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="s" s="2">
-        <v>29</v>
-      </c>
-      <c r="B4" t="s" s="2">
-        <v>35</v>
+      <c r="B4" t="s" s="2">
+        <v>34</v>
       </c>
     </row>
   </sheetData>
@@ -638,28 +633,28 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s" s="2">
         <v>26</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="s" s="2">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="s" s="2">
+    <row r="3">
+      <c r="A3" t="s" s="2">
+        <v>27</v>
+      </c>
+      <c r="B3" t="s" s="2">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s" s="2">
         <v>28</v>
       </c>
-      <c r="B3" t="s" s="2">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="s" s="2">
-        <v>29</v>
-      </c>
-      <c r="B4" t="s" s="2">
-        <v>36</v>
+      <c r="B4" t="s" s="2">
+        <v>35</v>
       </c>
     </row>
   </sheetData>
@@ -678,28 +673,28 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s" s="2">
         <v>26</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="s" s="2">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="s" s="2">
+    <row r="3">
+      <c r="A3" t="s" s="2">
+        <v>27</v>
+      </c>
+      <c r="B3" t="s" s="2">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s" s="2">
         <v>28</v>
       </c>
-      <c r="B3" t="s" s="2">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="s" s="2">
-        <v>29</v>
-      </c>
-      <c r="B4" t="s" s="2">
-        <v>37</v>
+      <c r="B4" t="s" s="2">
+        <v>36</v>
       </c>
     </row>
   </sheetData>
